--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98473</v>
+        <v>103923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>103918</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,32 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369939</v>
+        <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>92290</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,16 +1117,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545954</v>
+        <v>546035</v>
       </c>
       <c r="R6" t="n">
-        <v>6960281</v>
+        <v>6960320</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1167,6 +1170,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369935</v>
+        <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>91351</v>
+        <v>92295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1218,19 +1222,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546035</v>
+        <v>545954</v>
       </c>
       <c r="R7" t="n">
-        <v>6960320</v>
+        <v>6960281</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1271,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>103918</v>
+        <v>103923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>103918</v>
+        <v>103923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91651</v>
+        <v>91656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128369928</v>
+        <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100562</v>
+        <v>100567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546105</v>
+        <v>546104</v>
       </c>
       <c r="R12" t="n">
-        <v>6960345</v>
+        <v>6960332</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369930</v>
+        <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100562</v>
+        <v>100567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546104</v>
+        <v>546105</v>
       </c>
       <c r="R13" t="n">
-        <v>6960332</v>
+        <v>6960345</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>103918</v>
+        <v>103923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>103918</v>
+        <v>103923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>103923</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>104016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>103923</v>
+        <v>104016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>103923</v>
+        <v>104016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>103923</v>
+        <v>104016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>103923</v>
+        <v>104016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>104016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>104016</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>104016</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>104016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>104036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>104016</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100660</v>
+        <v>100674</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100660</v>
+        <v>100674</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>104057</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>104057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128369930</v>
+        <v>128369928</v>
       </c>
       <c r="B12" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546104</v>
+        <v>546105</v>
       </c>
       <c r="R12" t="n">
-        <v>6960332</v>
+        <v>6960345</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369928</v>
+        <v>128369930</v>
       </c>
       <c r="B13" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546105</v>
+        <v>546104</v>
       </c>
       <c r="R13" t="n">
-        <v>6960345</v>
+        <v>6960332</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>104087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>104060</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128369928</v>
+        <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546105</v>
+        <v>546104</v>
       </c>
       <c r="R12" t="n">
-        <v>6960345</v>
+        <v>6960332</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369930</v>
+        <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546104</v>
+        <v>546105</v>
       </c>
       <c r="R13" t="n">
-        <v>6960332</v>
+        <v>6960345</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>104087</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,32 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369935</v>
+        <v>128369939</v>
       </c>
       <c r="B6" t="n">
-        <v>91490</v>
+        <v>92439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,19 +1117,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546035</v>
+        <v>545954</v>
       </c>
       <c r="R6" t="n">
-        <v>6960320</v>
+        <v>6960281</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369939</v>
+        <v>128369935</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>91500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1222,16 +1218,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545954</v>
+        <v>546035</v>
       </c>
       <c r="R7" t="n">
-        <v>6960281</v>
+        <v>6960320</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1272,6 +1271,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104087</v>
+        <v>104100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104087</v>
+        <v>104100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91790</v>
+        <v>91800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100713</v>
+        <v>100726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100713</v>
+        <v>100726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104087</v>
+        <v>104100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104087</v>
+        <v>104100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1084,32 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369939</v>
+        <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>92439</v>
+        <v>91500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,16 +1117,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545954</v>
+        <v>546035</v>
       </c>
       <c r="R6" t="n">
-        <v>6960281</v>
+        <v>6960320</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1167,6 +1170,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369935</v>
+        <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>91500</v>
+        <v>92439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1218,19 +1222,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546035</v>
+        <v>545954</v>
       </c>
       <c r="R7" t="n">
-        <v>6960320</v>
+        <v>6960281</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1271,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>104104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,32 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369935</v>
+        <v>128369939</v>
       </c>
       <c r="B6" t="n">
-        <v>91500</v>
+        <v>92443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,19 +1117,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546035</v>
+        <v>545954</v>
       </c>
       <c r="R6" t="n">
-        <v>6960320</v>
+        <v>6960281</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369939</v>
+        <v>128369935</v>
       </c>
       <c r="B7" t="n">
-        <v>92439</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1222,16 +1218,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545954</v>
+        <v>546035</v>
       </c>
       <c r="R7" t="n">
-        <v>6960281</v>
+        <v>6960320</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1272,6 +1271,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B2" t="n">
-        <v>104104</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,37 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>104104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369937</v>
+        <v>128369932</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>104111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546010</v>
+        <v>546073</v>
       </c>
       <c r="R2" t="n">
-        <v>6960306</v>
+        <v>6960336</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369932</v>
+        <v>128369937</v>
       </c>
       <c r="B3" t="n">
-        <v>104104</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546073</v>
+        <v>546010</v>
       </c>
       <c r="R3" t="n">
-        <v>6960336</v>
+        <v>6960306</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>128369934</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128369927</v>
       </c>
       <c r="B5" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,32 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369939</v>
+        <v>128369935</v>
       </c>
       <c r="B6" t="n">
-        <v>92443</v>
+        <v>91509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,16 +1117,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545954</v>
+        <v>546035</v>
       </c>
       <c r="R6" t="n">
-        <v>6960281</v>
+        <v>6960320</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1167,6 +1170,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369935</v>
+        <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1218,19 +1222,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546035</v>
+        <v>545954</v>
       </c>
       <c r="R7" t="n">
-        <v>6960320</v>
+        <v>6960281</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1271,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>128369929</v>
       </c>
       <c r="B8" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>128369936</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>128369933</v>
       </c>
       <c r="B10" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128369940</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>128369930</v>
       </c>
       <c r="B12" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>128369928</v>
       </c>
       <c r="B13" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>128369931</v>
       </c>
       <c r="B14" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128369938</v>
       </c>
       <c r="B15" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128369932</v>
+        <v>128369940</v>
       </c>
       <c r="B2" t="n">
-        <v>104111</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546073</v>
+        <v>545954</v>
       </c>
       <c r="R2" t="n">
-        <v>6960336</v>
+        <v>6960294</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,49 +776,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369937</v>
+        <v>128369935</v>
       </c>
       <c r="B3" t="n">
-        <v>98643</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546010</v>
+        <v>546035</v>
       </c>
       <c r="R3" t="n">
-        <v>6960306</v>
+        <v>6960320</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -853,17 +856,13 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,52 +881,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369934</v>
+        <v>104000075</v>
       </c>
       <c r="B4" t="n">
-        <v>80134</v>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546063</v>
+        <v>545940</v>
       </c>
       <c r="R4" t="n">
-        <v>6960309</v>
+        <v>6960315</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,12 +946,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,68 +972,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369927</v>
+        <v>104000203</v>
       </c>
       <c r="B5" t="n">
-        <v>92448</v>
+        <v>93222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>3100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546102</v>
+        <v>545943</v>
       </c>
       <c r="R5" t="n">
-        <v>6960338</v>
+        <v>6960311</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1052,12 +1062,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,48 +1088,57 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369935</v>
+        <v>128369927</v>
       </c>
       <c r="B6" t="n">
-        <v>91509</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1117,19 +1146,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546035</v>
+        <v>546102</v>
       </c>
       <c r="R6" t="n">
-        <v>6960320</v>
+        <v>6960338</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,7 +1196,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1192,7 +1217,7 @@
         <v>128369939</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128369929</v>
+        <v>128369936</v>
       </c>
       <c r="B8" t="n">
-        <v>104111</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1329,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546099</v>
+        <v>546019</v>
       </c>
       <c r="R8" t="n">
-        <v>6960344</v>
+        <v>6960317</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369936</v>
+        <v>104000087</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,41 +1427,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546019</v>
+        <v>545937</v>
       </c>
       <c r="R9" t="n">
-        <v>6960317</v>
+        <v>6960321</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,12 +1481,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,48 +1507,57 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369933</v>
+        <v>128369934</v>
       </c>
       <c r="B10" t="n">
-        <v>104111</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1531,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546070</v>
+        <v>546063</v>
       </c>
       <c r="R10" t="n">
-        <v>6960317</v>
+        <v>6960309</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,37 +1633,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128369940</v>
+        <v>128369937</v>
       </c>
       <c r="B11" t="n">
-        <v>91809</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1632,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545954</v>
+        <v>546010</v>
       </c>
       <c r="R11" t="n">
-        <v>6960294</v>
+        <v>6960306</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1668,6 +1708,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128369930</v>
+        <v>128369929</v>
       </c>
       <c r="B12" t="n">
-        <v>100737</v>
+        <v>104628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,16 +1750,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1733,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546104</v>
+        <v>546099</v>
       </c>
       <c r="R12" t="n">
-        <v>6960332</v>
+        <v>6960344</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1795,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369928</v>
+        <v>128369931</v>
       </c>
       <c r="B13" t="n">
-        <v>100737</v>
+        <v>104628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,16 +1851,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1834,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546105</v>
+        <v>546097</v>
       </c>
       <c r="R13" t="n">
-        <v>6960345</v>
+        <v>6960325</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1896,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369931</v>
+        <v>128369932</v>
       </c>
       <c r="B14" t="n">
-        <v>104111</v>
+        <v>104628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546097</v>
+        <v>546073</v>
       </c>
       <c r="R14" t="n">
-        <v>6960325</v>
+        <v>6960336</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1997,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369938</v>
+        <v>128369933</v>
       </c>
       <c r="B15" t="n">
-        <v>104111</v>
+        <v>104628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545963</v>
+        <v>546070</v>
       </c>
       <c r="R15" t="n">
-        <v>6960268</v>
+        <v>6960317</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2095,6 +2140,425 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128369938</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>545963</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6960268</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128369928</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>546105</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6960345</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128369930</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>546104</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6960332</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104000117</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545939</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6960325</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369940</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369935</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000203</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369927</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369939</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369936</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000087</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369937</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369929</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369931</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369932</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369933</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2241,6 +2316,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369938</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2342,6 +2422,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369928</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2443,6 +2528,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369930</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2559,8 +2649,33 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>